--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95911</v>
+        <v>95914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95916</v>
+        <v>95922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95922</v>
+        <v>95925</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123251429</v>
       </c>
       <c r="B2" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95925</v>
+        <v>95942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123251429</v>
       </c>
       <c r="B2" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95942</v>
+        <v>95949</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6298-2025 artfynd.xlsx
+++ b/artfynd/A 6298-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123251426</v>
       </c>
       <c r="B3" t="n">
-        <v>95951</v>
+        <v>96332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
